--- a/sample_data/Incident.xlsx
+++ b/sample_data/Incident.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,17 +441,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VMS PART</t>
+          <t>TM PART</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>H사</t>
+          <t>S사</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -463,7 +463,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,19 +473,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>H사</t>
+          <t>D사</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>납품 로트 표면 결함 통보</t>
+          <t>치수 산포 이슈 제기</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>D사</t>
+          <t>K사</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -507,12 +507,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VMS PART</t>
+          <t>TM PART</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -522,14 +522,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>조립 간섭 클레임</t>
+          <t>포장 불량 접수</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>D사</t>
+          <t>H사</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -551,17 +551,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TM PART</t>
+          <t>VMS PART</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>H사</t>
+          <t>S사</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,19 +583,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>S사</t>
+          <t>D사</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>포장 불량 접수</t>
+          <t>소음 이상 보고</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -605,41 +605,41 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>K사</t>
+          <t>D사</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>포장 불량 접수</t>
+          <t>납품 로트 표면 결함 통보</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TM PART</t>
+          <t>VMS PART</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>S사</t>
+          <t>D사</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>조립 간섭 클레임</t>
+          <t>소음 이상 보고</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>K사</t>
+          <t>D사</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>포장 불량 접수</t>
+          <t>납품 로트 표면 결함 통보</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TM PART</t>
+          <t>VMS PART</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>소음 이상 보고</t>
+          <t>포장 불량 접수</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TM PART</t>
+          <t>VMS PART</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>S사</t>
+          <t>K사</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,41 +715,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>S사</t>
+          <t>H사</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>소음 이상 보고</t>
+          <t>치수 산포 이슈 제기</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VMS PART</t>
+          <t>TM PART</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>K사</t>
+          <t>D사</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>납품 로트 표면 결함 통보</t>
+          <t>포장 불량 접수</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -764,14 +764,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>치수 산포 이슈 제기</t>
+          <t>소음 이상 보고</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,144 +781,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>D사</t>
+          <t>K사</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>치수 산포 이슈 제기</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>TM PART</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>K사</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>치수 산포 이슈 제기</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>VMS PART</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>K사</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>치수 산포 이슈 제기</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>VMS PART</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>S사</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>조립 간섭 클레임</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>VMS PART</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>D사</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>납품 로트 표면 결함 통보</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>TM PART</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>K사</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>포장 불량 접수</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>TM PART</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>K사</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>치수 산포 이슈 제기</t>
+          <t>소음 이상 보고</t>
         </is>
       </c>
     </row>
